--- a/backend/data/ST1131_Quiz1.xlsx
+++ b/backend/data/ST1131_Quiz1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/extracted_questions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/dsa3101-2510-quiz-02/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA6C880-504B-FB42-B065-EFA3B21629F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB648FA6-2C52-084D-8207-7A74D7D6AD7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{CA20E2D9-AC26-2B4B-A400-E03C0BFEE2BC}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{CA20E2D9-AC26-2B4B-A400-E03C0BFEE2BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Context" sheetId="1" r:id="rId1"/>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="66">
-  <si>
-    <t>Context ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="67">
   <si>
     <t>Context Text</t>
   </si>
@@ -241,6 +238,12 @@
   </si>
   <si>
     <t>Basic Concepts in Statistics, EDA</t>
+  </si>
+  <si>
+    <t>Context ID</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -620,13 +623,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -649,52 +652,52 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
       <c r="P1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
@@ -702,10 +705,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -714,13 +717,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M2">
         <v>1</v>
       </c>
+      <c r="N2" t="s">
+        <v>66</v>
+      </c>
       <c r="O2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -728,10 +734,10 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -740,13 +746,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M3">
         <v>1</v>
       </c>
+      <c r="N3" t="s">
+        <v>66</v>
+      </c>
       <c r="O3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -754,10 +763,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -766,13 +775,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M4">
         <v>1</v>
       </c>
+      <c r="N4" t="s">
+        <v>66</v>
+      </c>
       <c r="O4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -780,10 +792,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -792,13 +804,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M5">
         <v>1</v>
       </c>
+      <c r="N5" t="s">
+        <v>66</v>
+      </c>
       <c r="O5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -806,10 +821,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -818,13 +833,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M6">
         <v>1</v>
       </c>
+      <c r="N6" t="s">
+        <v>66</v>
+      </c>
       <c r="O6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
@@ -832,60 +850,66 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
         <v>25</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>26</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>27</v>
       </c>
-      <c r="G7" t="s">
-        <v>28</v>
-      </c>
       <c r="K7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
+      <c r="N7" t="s">
+        <v>66</v>
+      </c>
       <c r="O7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" t="s">
+        <v>62</v>
+      </c>
+      <c r="P8" t="s">
         <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="O8" t="s">
-        <v>63</v>
-      </c>
-      <c r="P8" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
@@ -893,10 +917,10 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -905,13 +929,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
+      <c r="N9" t="s">
+        <v>66</v>
+      </c>
       <c r="O9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
@@ -919,34 +946,37 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
         <v>36</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" t="s">
         <v>42</v>
       </c>
-      <c r="F10" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" t="s">
-        <v>43</v>
-      </c>
       <c r="M10">
         <v>1</v>
       </c>
+      <c r="N10" t="s">
+        <v>66</v>
+      </c>
       <c r="O10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
@@ -954,10 +984,10 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
         <v>44</v>
-      </c>
-      <c r="E11" t="s">
-        <v>45</v>
       </c>
       <c r="K11">
         <v>20</v>
@@ -965,8 +995,11 @@
       <c r="M11">
         <v>1</v>
       </c>
+      <c r="N11" t="s">
+        <v>66</v>
+      </c>
       <c r="O11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
@@ -974,10 +1007,10 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -986,33 +1019,39 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
+      <c r="N12" t="s">
+        <v>66</v>
+      </c>
       <c r="O12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="409.5" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E13" t="s">
-        <v>45</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="M13">
         <v>1</v>
       </c>
+      <c r="N13" t="s">
+        <v>66</v>
+      </c>
       <c r="O13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -1020,10 +1059,10 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -1032,13 +1071,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M14">
         <v>1</v>
       </c>
+      <c r="N14" t="s">
+        <v>66</v>
+      </c>
       <c r="O14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
@@ -1046,10 +1088,10 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -1058,13 +1100,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M15">
         <v>1</v>
       </c>
+      <c r="N15" t="s">
+        <v>66</v>
+      </c>
       <c r="O15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
@@ -1072,25 +1117,28 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" t="s">
         <v>51</v>
       </c>
-      <c r="E16" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>52</v>
       </c>
-      <c r="G16" t="s">
-        <v>53</v>
-      </c>
       <c r="K16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
+      <c r="N16" t="s">
+        <v>66</v>
+      </c>
       <c r="O16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.2">
@@ -1098,31 +1146,34 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" t="s">
         <v>54</v>
       </c>
-      <c r="E17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" t="s">
-        <v>52</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>55</v>
       </c>
-      <c r="I17" t="s">
-        <v>56</v>
-      </c>
       <c r="K17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M17">
         <v>1</v>
       </c>
+      <c r="N17" t="s">
+        <v>66</v>
+      </c>
       <c r="O17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
@@ -1130,31 +1181,34 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" t="s">
         <v>55</v>
       </c>
-      <c r="I18" t="s">
-        <v>56</v>
-      </c>
       <c r="K18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M18">
         <v>1</v>
       </c>
+      <c r="N18" t="s">
+        <v>66</v>
+      </c>
       <c r="O18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
